--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,9 +804,235 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136765747</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93425</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Flögberget, Flögberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>655297</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6945120</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Inga-Greta Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Inga-Greta Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136765747</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136765780</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93435</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flögberget, Flögberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>655297</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6945120</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inga-Greta Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inga-Greta Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136765780</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8921-2024 artfynd.xlsx
+++ b/artfynd/A 8921-2024 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>136765747</v>
       </c>
       <c r="B3" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136765780</v>
       </c>
       <c r="B4" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
